--- a/data/raw data/input_default_values_sources.xlsx
+++ b/data/raw data/input_default_values_sources.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rotenle/Documents/MetC_Locals/MTS/transport-emission-shiny/data/raw data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icfonline-my.sharepoint.com/personal/61886_icf_com/Documents/Desktop/transport-emission-shiny-metc-review/data/raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{42A49635-D1DB-864B-8A2F-78AB05832A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:9_{42A49635-D1DB-864B-8A2F-78AB05832A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4524C68E-7F41-49B5-BA06-A2E2E1D1DED2}"/>
   <bookViews>
-    <workbookView xWindow="5820" yWindow="5340" windowWidth="31960" windowHeight="16940" xr2:uid="{9F3C916E-6CEA-B948-AC4B-7F24B434A037}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F3C916E-6CEA-B948-AC4B-7F24B434A037}"/>
   </bookViews>
   <sheets>
     <sheet name="input_default_values" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">input_default_values!$A$1:$G$81</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="168">
   <si>
     <t>ID</t>
   </si>
@@ -512,13 +515,25 @@
   </si>
   <si>
     <t>See MetCouncil Tables &gt; Default Timeline</t>
+  </si>
+  <si>
+    <t>Task 4 Recommendation Methodology Table 23. Recommended Methodology for EV Edication and Outreach</t>
+  </si>
+  <si>
+    <t>See MetCouncil Tables &gt; Charger Utilization Rates And Power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See Fleet Data, stock_percentages.R script </t>
+  </si>
+  <si>
+    <t xml:space="preserve">See MetCouncil Tables &gt; Adjustment Factors and Trip Lengths </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1021,12 +1036,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1403,16 +1421,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67EF9C0F-5982-F946-A95E-564EC6E4D1C3}">
   <dimension ref="A1:G81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="27.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.125" customWidth="1"/>
+    <col min="6" max="6" width="23.25" customWidth="1"/>
+    <col min="7" max="7" width="73.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
@@ -1435,7 +1455,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="31.5">
       <c r="A2" t="s">
         <v>36</v>
       </c>
@@ -1454,8 +1474,11 @@
       <c r="F2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="G2" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -1478,7 +1501,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -1501,7 +1524,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1524,7 +1547,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="31.5">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="F6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="G6" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -1563,8 +1589,11 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -1587,7 +1616,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -1606,8 +1635,11 @@
       <c r="F9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -1627,7 +1659,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1647,7 +1679,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1670,7 +1702,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1693,7 +1725,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1712,8 +1744,11 @@
       <c r="F14" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -1732,8 +1767,11 @@
       <c r="F15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="G15" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -1752,8 +1790,11 @@
       <c r="F16" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+      <c r="G16" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -1773,7 +1814,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -1796,7 +1837,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1816,7 +1857,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -1839,7 +1880,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1862,7 +1903,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -1882,7 +1923,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -1902,7 +1943,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -1922,7 +1963,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -1942,7 +1983,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1965,7 +2006,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -1985,7 +2026,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -2005,7 +2046,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -2028,7 +2069,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -2048,7 +2089,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2068,7 +2109,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -2088,7 +2129,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -2111,7 +2152,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -2131,7 +2172,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>74</v>
       </c>
@@ -2154,7 +2195,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -2177,7 +2218,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>74</v>
       </c>
@@ -2197,7 +2238,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -2217,7 +2258,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2237,7 +2278,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2260,7 +2301,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>74</v>
       </c>
@@ -2280,7 +2321,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -2300,7 +2341,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>74</v>
       </c>
@@ -2323,7 +2364,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>74</v>
       </c>
@@ -2343,7 +2384,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>74</v>
       </c>
@@ -2363,7 +2404,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -2383,7 +2424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>74</v>
       </c>
@@ -2403,7 +2444,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -2423,7 +2464,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>105</v>
       </c>
@@ -2443,7 +2484,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>105</v>
       </c>
@@ -2466,7 +2507,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>105</v>
       </c>
@@ -2489,7 +2530,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>105</v>
       </c>
@@ -2509,7 +2550,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>105</v>
       </c>
@@ -2529,7 +2570,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>105</v>
       </c>
@@ -2549,7 +2590,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>105</v>
       </c>
@@ -2569,7 +2610,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>105</v>
       </c>
@@ -2589,7 +2630,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>105</v>
       </c>
@@ -2609,7 +2650,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>105</v>
       </c>
@@ -2629,7 +2670,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>105</v>
       </c>
@@ -2649,7 +2690,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>105</v>
       </c>
@@ -2669,7 +2710,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>105</v>
       </c>
@@ -2692,7 +2733,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>105</v>
       </c>
@@ -2712,7 +2753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>105</v>
       </c>
@@ -2732,7 +2773,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>105</v>
       </c>
@@ -2752,7 +2793,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>105</v>
       </c>
@@ -2772,7 +2813,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>105</v>
       </c>
@@ -2792,7 +2833,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>105</v>
       </c>
@@ -2812,7 +2853,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>136</v>
       </c>
@@ -2835,7 +2876,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>136</v>
       </c>
@@ -2855,7 +2896,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>136</v>
       </c>
@@ -2875,7 +2916,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>136</v>
       </c>
@@ -2898,7 +2939,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>136</v>
       </c>
@@ -2918,7 +2959,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>136</v>
       </c>
@@ -2938,7 +2979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>136</v>
       </c>
@@ -2958,7 +2999,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>136</v>
       </c>
@@ -2981,7 +3022,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>136</v>
       </c>
@@ -3001,7 +3042,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>136</v>
       </c>
@@ -3021,7 +3062,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>136</v>
       </c>
@@ -3044,7 +3085,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>136</v>
       </c>
@@ -3064,7 +3105,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>136</v>
       </c>
@@ -3084,7 +3125,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>136</v>
       </c>
@@ -3105,6 +3146,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G81" xr:uid="{67EF9C0F-5982-F946-A95E-564EC6E4D1C3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/raw data/input_default_values_sources.xlsx
+++ b/data/raw data/input_default_values_sources.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icfonline-my.sharepoint.com/personal/61886_icf_com/Documents/Desktop/transport-emission-shiny-metc-review/data/raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:9_{42A49635-D1DB-864B-8A2F-78AB05832A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4524C68E-7F41-49B5-BA06-A2E2E1D1DED2}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:9_{42A49635-D1DB-864B-8A2F-78AB05832A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3F9D59C-1A1B-40CB-80C5-6616D643CE16}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F3C916E-6CEA-B948-AC4B-7F24B434A037}"/>
+    <workbookView xWindow="4425" yWindow="0" windowWidth="24405" windowHeight="15585" xr2:uid="{9F3C916E-6CEA-B948-AC4B-7F24B434A037}"/>
   </bookViews>
   <sheets>
     <sheet name="input_default_values" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">input_default_values!$A$1:$G$81</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="173">
   <si>
     <t>ID</t>
   </si>
@@ -517,9 +530,6 @@
     <t>See MetCouncil Tables &gt; Default Timeline</t>
   </si>
   <si>
-    <t>Task 4 Recommendation Methodology Table 23. Recommended Methodology for EV Edication and Outreach</t>
-  </si>
-  <si>
     <t>See MetCouncil Tables &gt; Charger Utilization Rates And Power</t>
   </si>
   <si>
@@ -527,6 +537,24 @@
   </si>
   <si>
     <t xml:space="preserve">See MetCouncil Tables &gt; Adjustment Factors and Trip Lengths </t>
+  </si>
+  <si>
+    <t>See MetCouncil Tables &gt; Charger Utilization Rates and Power</t>
+  </si>
+  <si>
+    <t>See MetCouncil Tables &gt; Total VMT Reduction Potential</t>
+  </si>
+  <si>
+    <t>See MetCouncil Tables &gt; VMT by Community Type</t>
+  </si>
+  <si>
+    <t>Task 4 Recommendation Methodology Table 23. Recommended Methodology for Shared Mobility</t>
+  </si>
+  <si>
+    <t>Task 4 Recommendation Methodology Table 23. Recommended Methodology for 1.1.1 Multi-Use Trails and Bicycle Facilities</t>
+  </si>
+  <si>
+    <t>Task 4 Recommendation Methodology Table 23. Recommended Methodology for EV Education and Outreach</t>
   </si>
 </sst>
 </file>
@@ -1475,7 +1503,7 @@
         <v>32</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1567,7 +1595,7 @@
         <v>32</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1658,6 +1686,9 @@
       <c r="F10" t="s">
         <v>32</v>
       </c>
+      <c r="G10" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
@@ -1678,6 +1709,9 @@
       <c r="F11" t="s">
         <v>32</v>
       </c>
+      <c r="G11" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
@@ -1745,7 +1779,7 @@
         <v>32</v>
       </c>
       <c r="G14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1768,7 +1802,7 @@
         <v>32</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1791,7 +1825,7 @@
         <v>33</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1813,6 +1847,9 @@
       <c r="F17" t="s">
         <v>33</v>
       </c>
+      <c r="G17" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
@@ -1856,6 +1893,9 @@
       <c r="F19" t="s">
         <v>32</v>
       </c>
+      <c r="G19" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
@@ -1922,6 +1962,9 @@
       <c r="F22" t="s">
         <v>32</v>
       </c>
+      <c r="G22" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
@@ -1942,6 +1985,9 @@
       <c r="F23" t="s">
         <v>32</v>
       </c>
+      <c r="G23" s="1" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
@@ -1962,6 +2008,9 @@
       <c r="F24" t="s">
         <v>32</v>
       </c>
+      <c r="G24" s="1" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
@@ -1982,6 +2031,9 @@
       <c r="F25" t="s">
         <v>61</v>
       </c>
+      <c r="G25" s="1" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
@@ -2025,6 +2077,9 @@
       <c r="F27" t="s">
         <v>32</v>
       </c>
+      <c r="G27" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
@@ -2045,6 +2100,9 @@
       <c r="F28" t="s">
         <v>33</v>
       </c>
+      <c r="G28" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
@@ -2088,6 +2146,9 @@
       <c r="F30" t="s">
         <v>32</v>
       </c>
+      <c r="G30" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
@@ -2108,6 +2169,9 @@
       <c r="F31" t="s">
         <v>32</v>
       </c>
+      <c r="G31" s="1" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
@@ -2128,6 +2192,9 @@
       <c r="F32" t="s">
         <v>32</v>
       </c>
+      <c r="G32" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
@@ -2171,6 +2238,9 @@
       <c r="F34" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="G34" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
@@ -2237,6 +2307,9 @@
       <c r="F37" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="G37" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
@@ -2257,6 +2330,9 @@
       <c r="F38" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="G38" s="4" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
@@ -2277,6 +2353,9 @@
       <c r="F39" t="s">
         <v>33</v>
       </c>
+      <c r="G39" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
@@ -2320,6 +2399,9 @@
       <c r="F41" t="s">
         <v>32</v>
       </c>
+      <c r="G41" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
@@ -2340,6 +2422,9 @@
       <c r="F42" t="s">
         <v>33</v>
       </c>
+      <c r="G42" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
@@ -2383,6 +2468,9 @@
       <c r="F44" t="s">
         <v>32</v>
       </c>
+      <c r="G44" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
@@ -2403,6 +2491,9 @@
       <c r="F45" t="s">
         <v>32</v>
       </c>
+      <c r="G45" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
@@ -2423,6 +2514,9 @@
       <c r="F46" t="s">
         <v>32</v>
       </c>
+      <c r="G46" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
@@ -2438,13 +2532,16 @@
         <v>101</v>
       </c>
       <c r="E47">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="F47" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="G47" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="31.5">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -2462,6 +2559,9 @@
       </c>
       <c r="F48" t="s">
         <v>32</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2483,6 +2583,9 @@
       <c r="F49" t="s">
         <v>108</v>
       </c>
+      <c r="G49" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
@@ -2549,6 +2652,9 @@
       <c r="F52" t="s">
         <v>32</v>
       </c>
+      <c r="G52" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
@@ -2569,6 +2675,9 @@
       <c r="F53" t="s">
         <v>32</v>
       </c>
+      <c r="G53" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
@@ -2589,6 +2698,9 @@
       <c r="F54" t="s">
         <v>32</v>
       </c>
+      <c r="G54" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
@@ -2609,6 +2721,9 @@
       <c r="F55" t="s">
         <v>32</v>
       </c>
+      <c r="G55" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
@@ -2629,8 +2744,11 @@
       <c r="F56" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="57" spans="1:7">
+      <c r="G56" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="31.5">
       <c r="A57" t="s">
         <v>105</v>
       </c>
@@ -2648,6 +2766,9 @@
       </c>
       <c r="F57" t="s">
         <v>32</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2669,6 +2790,9 @@
       <c r="F58" t="s">
         <v>108</v>
       </c>
+      <c r="G58" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
@@ -2689,6 +2813,9 @@
       <c r="F59" t="s">
         <v>108</v>
       </c>
+      <c r="G59" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
@@ -2709,6 +2836,9 @@
       <c r="F60" t="s">
         <v>108</v>
       </c>
+      <c r="G60" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
@@ -2752,6 +2882,9 @@
       <c r="F62" t="s">
         <v>32</v>
       </c>
+      <c r="G62" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
@@ -2772,6 +2905,9 @@
       <c r="F63" t="s">
         <v>32</v>
       </c>
+      <c r="G63" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
@@ -2792,6 +2928,9 @@
       <c r="F64" t="s">
         <v>32</v>
       </c>
+      <c r="G64" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
@@ -2812,6 +2951,9 @@
       <c r="F65" t="s">
         <v>32</v>
       </c>
+      <c r="G65" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
@@ -2832,8 +2974,11 @@
       <c r="F66" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="67" spans="1:7">
+      <c r="G66" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="31.5">
       <c r="A67" t="s">
         <v>105</v>
       </c>
@@ -2851,6 +2996,9 @@
       </c>
       <c r="F67" t="s">
         <v>32</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2895,6 +3043,9 @@
       <c r="F69" t="s">
         <v>32</v>
       </c>
+      <c r="G69" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
@@ -2915,6 +3066,9 @@
       <c r="F70" t="s">
         <v>108</v>
       </c>
+      <c r="G70" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
@@ -2958,6 +3112,9 @@
       <c r="F72" t="s">
         <v>32</v>
       </c>
+      <c r="G72" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
@@ -2978,6 +3135,9 @@
       <c r="F73" t="s">
         <v>32</v>
       </c>
+      <c r="G73" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
@@ -2998,6 +3158,9 @@
       <c r="F74" t="s">
         <v>32</v>
       </c>
+      <c r="G74" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
@@ -3041,6 +3204,9 @@
       <c r="F76" t="s">
         <v>32</v>
       </c>
+      <c r="G76" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
@@ -3061,6 +3227,9 @@
       <c r="F77" t="s">
         <v>108</v>
       </c>
+      <c r="G77" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
@@ -3104,6 +3273,9 @@
       <c r="F79" t="s">
         <v>32</v>
       </c>
+      <c r="G79" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
@@ -3124,8 +3296,11 @@
       <c r="F80" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="G80" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>136</v>
       </c>
@@ -3143,6 +3318,9 @@
       </c>
       <c r="F81" t="s">
         <v>32</v>
+      </c>
+      <c r="G81" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
